--- a/Instrument_tree.xlsx
+++ b/Instrument_tree.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Axel\PYTHON\FragHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6349F7A3-53C4-4350-AF5D-171651E5F29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAF4291-818D-48B7-BAEF-D188AD6F7DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AB SCIEX" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="323">
   <si>
     <t>MARQUES</t>
   </si>
@@ -1008,6 +1011,9 @@
   </si>
   <si>
     <t>EB</t>
+  </si>
+  <si>
+    <t>Excedion Pro</t>
   </si>
 </sst>
 </file>
@@ -3598,7 +3604,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -4633,10 +4639,48 @@
       <c r="G51" s="3"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="3"/>
+      <c r="A52" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>52</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
